--- a/Result/profitability/5515.xlsx
+++ b/Result/profitability/5515.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01375</v>
+        <v>1.44375</v>
       </c>
       <c r="N2" t="n">
-        <v>15.1425</v>
+        <v>16.08</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.78</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02625</v>
+        <v>1.4375</v>
       </c>
       <c r="N3" t="n">
-        <v>15.0975</v>
+        <v>15.66375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9825</v>
+        <v>1.44</v>
       </c>
       <c r="N4" t="n">
-        <v>14.80125</v>
+        <v>15.3075</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9812500000000001</v>
+        <v>1.46625</v>
       </c>
       <c r="N5" t="n">
-        <v>14.80125</v>
+        <v>15.71</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.99625</v>
+        <v>1.235</v>
       </c>
       <c r="N6" t="n">
-        <v>15.09875</v>
+        <v>14.97375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8025</v>
+        <v>1.12125</v>
       </c>
       <c r="N7" t="n">
-        <v>14.075</v>
+        <v>14.23375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.66875</v>
+        <v>0.93875</v>
       </c>
       <c r="N8" t="n">
-        <v>13.68</v>
+        <v>13.66875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5515</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1617</v>
+      </c>
+      <c r="E75" t="n">
+        <v>387</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>236</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>694</v>
+      </c>
+      <c r="J75" t="n">
+        <v>930</v>
+      </c>
+      <c r="K75" t="n">
+        <v>831</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.50875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.37875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.102040816326531</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.08999999999999986</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.004636785162287493</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>16.16666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6033195020746887</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
